--- a/исправления внести/эниология.xlsx
+++ b/исправления внести/эниология.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\исправления внести\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\исправления внести\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3C815D3-9A88-460D-B900-520CBCE38E76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{640854D4-7762-440A-99DA-E4CE4F5AA025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25710" yWindow="2110" windowWidth="25820" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="после перевода" sheetId="2" r:id="rId1"/>
@@ -24,15 +24,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="289">
   <si>
     <t>Наступила период</t>
   </si>
@@ -842,9 +839,6 @@
   </si>
   <si>
     <t>мольберт,</t>
-  </si>
-  <si>
-    <t>тренировках,</t>
   </si>
   <si>
     <t>эниологической</t>
@@ -1237,79 +1231,79 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F21563D1-1294-476A-895B-8DF86C2F507F}">
   <dimension ref="A1:A14"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="23.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A3" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A6" t="s">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A7" t="s">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A8" t="s">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A9" t="s">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A10" t="s">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A11" t="s">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>288</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A12" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A13" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A14" t="s">
-        <v>289</v>
       </c>
     </row>
   </sheetData>
@@ -1320,1439 +1314,1434 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F65167D-C510-40BD-B401-AA5A335D9CBB}">
   <dimension ref="A2:A287"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="29.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="133" spans="1:1" ht="15.75" x14ac:dyDescent="0.75">
+    <row r="133" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A133" s="2" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="180" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="181" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="182" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="183" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="184" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="185" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="186" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="187" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="188" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="189" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="190" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="191" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="192" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="193" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="194" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="195" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="196" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="197" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="198" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="199" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="200" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="201" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="202" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="202" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="203" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="203" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="204" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="204" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="205" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="205" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="206" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="206" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="207" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="207" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="208" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="208" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="209" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="209" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="210" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="210" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="211" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="211" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="212" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="212" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="213" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="213" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="214" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="214" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="215" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="215" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="216" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="216" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="217" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="217" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="218" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="218" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="219" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="219" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="220" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="220" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="221" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="221" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="222" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="222" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="223" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="223" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="224" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="224" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="225" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="225" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="226" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="226" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="227" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="227" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="228" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="228" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="229" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="229" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="230" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="230" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="231" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="231" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="232" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="232" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="233" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="233" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="234" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="234" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="235" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="235" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="236" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="236" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="237" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="237" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="238" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="238" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="239" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="239" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="240" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="240" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="241" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="241" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="242" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="242" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="243" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="243" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="244" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="244" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="245" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="245" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="246" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="246" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="247" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="247" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="248" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="248" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="249" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="249" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="250" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="250" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="251" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="251" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="252" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="252" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="253" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="253" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="254" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="254" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="255" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="255" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="256" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="256" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="257" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="257" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="258" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="258" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="259" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="259" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="260" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="260" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="261" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="261" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="262" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="262" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="263" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="263" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="264" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="264" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="265" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="265" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="266" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="266" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="267" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="267" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="268" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="268" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="269" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="269" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="270" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="270" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="271" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="271" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="272" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="272" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="273" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="273" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="274" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="274" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="275" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="275" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="276" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="276" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="277" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="277" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="278" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="278" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="279" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="279" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="280" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A280" t="s">
+    <row r="281" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A281" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="281" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A281" t="s">
+    <row r="282" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A282" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="282" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A282" t="s">
+    <row r="283" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A283" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="283" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A283" t="s">
+    <row r="284" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A284" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="284" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A284" t="s">
+    <row r="285" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A285" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="285" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A285" t="s">
+    <row r="286" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A286" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="286" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A286" t="s">
+    <row r="287" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A287" t="s">
         <v>276</v>
-      </c>
-    </row>
-    <row r="287" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A287" t="s">
-        <v>277</v>
       </c>
     </row>
   </sheetData>

--- a/исправления внести/эниология.xlsx
+++ b/исправления внести/эниология.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\исправления внести\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\исправления внести\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{640854D4-7762-440A-99DA-E4CE4F5AA025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D77E8DA-B649-4ABE-8F3E-0F22FC9614BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-7990" yWindow="2220" windowWidth="8080" windowHeight="10170" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="после перевода" sheetId="2" r:id="rId1"/>
@@ -24,15 +24,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="289">
-  <si>
-    <t>Наступила период</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="307">
   <si>
     <t>пресс-конференцию</t>
   </si>
@@ -877,25 +877,82 @@
     <t>Уровень духовной колдовства</t>
   </si>
   <si>
-    <t>углового особенности вращения</t>
-  </si>
-  <si>
     <t>энергетики,</t>
   </si>
   <si>
     <t>коммуникаций</t>
   </si>
   <si>
-    <t>«третьего очи»,</t>
-  </si>
-  <si>
     <t>гуру</t>
   </si>
   <si>
-    <t>международной разряды,</t>
-  </si>
-  <si>
-    <t>земной общества.</t>
+    <t>компании</t>
+  </si>
+  <si>
+    <t>прессе?</t>
+  </si>
+  <si>
+    <t>физического</t>
+  </si>
+  <si>
+    <t>спектакль</t>
+  </si>
+  <si>
+    <t>фигурку</t>
+  </si>
+  <si>
+    <t>орбиту.</t>
+  </si>
+  <si>
+    <t>эпитаксиально</t>
+  </si>
+  <si>
+    <t>лазера»),</t>
+  </si>
+  <si>
+    <t>энергетически</t>
+  </si>
+  <si>
+    <t>меридиана</t>
+  </si>
+  <si>
+    <t>модулирует</t>
+  </si>
+  <si>
+    <t>модулятора</t>
+  </si>
+  <si>
+    <t>сотрапезники</t>
+  </si>
+  <si>
+    <t>симпатизирующие</t>
+  </si>
+  <si>
+    <t>несимпатизирующие</t>
+  </si>
+  <si>
+    <t>энергоцентр</t>
+  </si>
+  <si>
+    <t>подвыпившая предприятие</t>
+  </si>
+  <si>
+    <t>интуитивно</t>
+  </si>
+  <si>
+    <t>листке</t>
+  </si>
+  <si>
+    <t>маги.</t>
+  </si>
+  <si>
+    <t>сгенерируйте</t>
+  </si>
+  <si>
+    <t>сгенерированных</t>
+  </si>
+  <si>
+    <t>зафиксируйте</t>
   </si>
 </sst>
 </file>
@@ -1230,80 +1287,60 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F21563D1-1294-476A-895B-8DF86C2F507F}">
-  <dimension ref="A1:A14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A2:A12"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="23.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A3" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A5" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A6" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A7" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A9" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A10" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A11" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A12" t="s">
         <v>283</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>288</v>
       </c>
     </row>
   </sheetData>
@@ -1313,1435 +1350,1565 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F65167D-C510-40BD-B401-AA5A335D9CBB}">
-  <dimension ref="A2:A287"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A2:A312"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="29.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A9" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A13" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A14" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A15" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A16" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A17" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A18" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A19" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A20" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A21" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A22" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A23" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A24" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A25" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A26" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A27" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A28" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A29" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A30" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A31" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A32" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A33" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A34" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A35" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A36" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A37" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A38" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A39" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A40" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A41" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A42" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A43" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A44" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A45" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A46" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A47" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A48" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A49" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A50" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A51" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A52" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A53" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A53" t="s">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A54" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A55" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A55" t="s">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A56" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A56" t="s">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A57" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A57" t="s">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A58" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A58" t="s">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A59" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A59" t="s">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A60" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A60" t="s">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A61" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A61" t="s">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A62" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A62" t="s">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A63" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A63" t="s">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A64" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A64" t="s">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A65" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A65" t="s">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A66" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A66" t="s">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A67" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A67" t="s">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A68" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A68" t="s">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A69" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A69" t="s">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A70" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A70" t="s">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A71" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A71" t="s">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A72" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A72" t="s">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A73" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A73" t="s">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A74" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A74" t="s">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A75" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A75" t="s">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A76" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A76" t="s">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A77" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A77" t="s">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A78" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A78" t="s">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A79" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A79" t="s">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A80" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A80" t="s">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A81" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A81" t="s">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A82" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A82" t="s">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A83" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A83" t="s">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A84" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A84" t="s">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A85" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A85" t="s">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A86" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A86" t="s">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A87" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A87" t="s">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A88" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A88" t="s">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A89" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A89" t="s">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A90" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A90" t="s">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A91" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A91" t="s">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A92" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A92" t="s">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A93" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A93" t="s">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A94" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A94" t="s">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A95" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A95" t="s">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A96" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A96" t="s">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A97" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A97" t="s">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A98" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A98" t="s">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A99" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A99" t="s">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A100" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A100" t="s">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A101" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A101" t="s">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A102" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A102" t="s">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A103" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A103" t="s">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A104" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A104" t="s">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A105" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A105" t="s">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A106" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A106" t="s">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A107" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A107" t="s">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A108" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A108" t="s">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A109" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A109" t="s">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A110" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A110" t="s">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A111" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A111" t="s">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A112" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A112" t="s">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A113" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A113" t="s">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A114" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A114" t="s">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A115" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A115" t="s">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A116" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A116" t="s">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A117" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A117" t="s">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A118" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A118" t="s">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A119" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A119" t="s">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A120" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A120" t="s">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A121" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A121" t="s">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A122" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A122" t="s">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A123" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A123" t="s">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A124" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A124" t="s">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A125" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A125" t="s">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A126" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A126" t="s">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A127" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A127" t="s">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A128" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A128" t="s">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A129" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A129" t="s">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A130" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A130" t="s">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A131" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A131" t="s">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A132" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A132" t="s">
+    <row r="133" spans="1:1" ht="15.75" x14ac:dyDescent="0.75">
+      <c r="A133" s="2" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="133" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A133" s="2" t="s">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A134" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A134" t="s">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A135" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A135" t="s">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A136" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A136" t="s">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A137" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A137" t="s">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A138" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A138" t="s">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A139" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A139" t="s">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A140" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A140" t="s">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A141" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A141" t="s">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A142" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A142" t="s">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A143" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A143" t="s">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A144" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A144" t="s">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A145" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A145" t="s">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A146" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A146" t="s">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A147" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A147" t="s">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A148" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A148" t="s">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A149" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A149" t="s">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A150" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A150" t="s">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A151" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A151" t="s">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A152" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A152" t="s">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A153" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A153" t="s">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A154" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A154" t="s">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A155" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A155" t="s">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A156" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A156" t="s">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A157" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A157" t="s">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A158" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A158" t="s">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A159" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A159" t="s">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A160" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A160" t="s">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A161" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A161" t="s">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A162" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A162" t="s">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A163" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A163" t="s">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A164" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A164" t="s">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A165" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A165" t="s">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A166" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A166" t="s">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A167" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A167" t="s">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A168" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A168" t="s">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A169" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A169" t="s">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A170" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A170" t="s">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A171" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A171" t="s">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A172" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A172" t="s">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A173" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A173" t="s">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A174" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A174" t="s">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A175" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A175" t="s">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A176" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A176" t="s">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A177" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A177" t="s">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A178" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A178" t="s">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A179" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A179" t="s">
+    <row r="180" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A180" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A180" t="s">
+    <row r="181" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A181" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A182" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A181" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A182" t="s">
+    <row r="183" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A183" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A183" t="s">
+    <row r="184" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A184" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A184" t="s">
+    <row r="185" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A185" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A185" t="s">
+    <row r="186" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A186" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A186" t="s">
+    <row r="187" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A187" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A187" t="s">
+    <row r="188" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A188" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A188" t="s">
+    <row r="189" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A189" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A189" t="s">
+    <row r="190" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A190" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A190" t="s">
+    <row r="191" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A191" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A191" t="s">
+    <row r="192" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A192" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A192" t="s">
+    <row r="193" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A193" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A193" t="s">
+    <row r="194" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A194" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A194" t="s">
+    <row r="195" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A195" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A195" t="s">
+    <row r="196" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A196" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A196" t="s">
+    <row r="197" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A197" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A197" t="s">
+    <row r="198" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A198" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A198" t="s">
+    <row r="199" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A199" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A199" t="s">
+    <row r="200" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A200" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A200" t="s">
+    <row r="201" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A201" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A201" t="s">
+    <row r="202" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A202" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="202" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A202" t="s">
+    <row r="203" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A203" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A204" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="203" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A203" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="204" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A204" t="s">
+    <row r="205" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A205" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="205" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A205" t="s">
+    <row r="206" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A206" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A207" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A208" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A209" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="206" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A206" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="207" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A207" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="208" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A208" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="209" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A209" t="s">
+    <row r="210" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A210" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="210" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A210" t="s">
+    <row r="211" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A211" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="211" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A211" t="s">
+    <row r="212" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A212" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="212" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A212" t="s">
+    <row r="213" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A213" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="213" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A213" t="s">
+    <row r="214" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A214" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="214" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A214" t="s">
+    <row r="215" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A215" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="215" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A215" t="s">
+    <row r="216" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A216" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="216" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A216" t="s">
+    <row r="217" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A217" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="217" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A217" t="s">
+    <row r="218" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A218" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="218" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A218" t="s">
+    <row r="219" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A219" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="219" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A219" t="s">
+    <row r="220" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A220" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="220" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A220" t="s">
+    <row r="221" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A221" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="221" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A221" t="s">
+    <row r="222" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A222" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="222" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A222" t="s">
+    <row r="223" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A223" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="223" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A223" t="s">
+    <row r="224" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A224" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="224" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A224" t="s">
+    <row r="225" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A225" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="225" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A225" t="s">
+    <row r="226" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A226" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="226" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A226" t="s">
+    <row r="227" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A227" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="227" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A227" t="s">
+    <row r="228" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A228" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="228" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A228" t="s">
+    <row r="229" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A229" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="229" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A229" t="s">
+    <row r="230" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A230" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="230" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A230" t="s">
+    <row r="231" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A231" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="231" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A231" t="s">
+    <row r="232" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A232" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="232" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A232" t="s">
+    <row r="233" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A233" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="233" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A233" t="s">
+    <row r="234" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A234" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="234" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A234" t="s">
+    <row r="235" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A235" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="235" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A235" t="s">
+    <row r="236" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A236" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="236" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A236" t="s">
+    <row r="237" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A237" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="237" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A237" t="s">
+    <row r="238" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A238" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="238" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A238" t="s">
+    <row r="239" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A239" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="239" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A239" t="s">
+    <row r="240" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A240" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="240" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A240" t="s">
+    <row r="241" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A241" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="241" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A241" t="s">
+    <row r="242" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A242" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="242" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A242" t="s">
+    <row r="243" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A243" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="243" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A243" t="s">
+    <row r="244" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A244" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="244" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A244" t="s">
+    <row r="245" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A245" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="245" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A245" t="s">
+    <row r="246" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A246" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="246" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A246" t="s">
+    <row r="247" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A247" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="247" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A247" t="s">
+    <row r="248" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A248" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="248" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A248" t="s">
+    <row r="249" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A249" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="249" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A249" t="s">
+    <row r="250" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A250" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="250" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A250" t="s">
+    <row r="251" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A251" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="251" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A251" t="s">
+    <row r="252" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A252" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="252" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A252" t="s">
+    <row r="253" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A253" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="253" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A253" t="s">
+    <row r="254" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A254" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="254" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A254" t="s">
+    <row r="255" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A255" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="255" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A255" t="s">
+    <row r="256" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A256" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="256" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A256" t="s">
+    <row r="257" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A257" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="257" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A257" t="s">
+    <row r="258" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A258" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="258" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A258" t="s">
+    <row r="259" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A259" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="259" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A259" t="s">
+    <row r="260" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A260" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="260" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A260" t="s">
+    <row r="261" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A261" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="261" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A261" t="s">
+    <row r="262" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A262" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="262" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A262" t="s">
+    <row r="263" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A263" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="263" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A263" t="s">
+    <row r="264" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A264" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="264" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A264" t="s">
+    <row r="265" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A265" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="265" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A265" t="s">
+    <row r="266" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A266" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="266" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A266" t="s">
+    <row r="267" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A267" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="267" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A267" t="s">
+    <row r="268" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A268" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="268" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A268" t="s">
+    <row r="269" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A269" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="269" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A269" t="s">
+    <row r="270" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A270" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="270" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A270" t="s">
+    <row r="271" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A271" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="271" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A271" t="s">
+    <row r="272" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A272" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="273" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A273" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="272" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A272" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="273" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A273" t="s">
+    <row r="274" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A274" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="274" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A274" t="s">
+    <row r="275" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A275" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="275" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A275" t="s">
+    <row r="276" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A276" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="276" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A276" t="s">
+    <row r="277" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A277" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="277" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A277" t="s">
+    <row r="278" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A278" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="278" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A278" t="s">
+    <row r="279" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A279" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="279" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A279" t="s">
+    <row r="280" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A280" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="281" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A281" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="281" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A281" t="s">
+    <row r="282" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A282" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="282" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A282" t="s">
+    <row r="283" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A283" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="283" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A283" t="s">
+    <row r="284" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A284" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="284" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A284" t="s">
+    <row r="285" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A285" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="285" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A285" t="s">
+    <row r="286" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A286" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="286" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A286" t="s">
+    <row r="287" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A287" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="287" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A287" t="s">
-        <v>276</v>
+    <row r="288" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A288" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="289" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A289" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="290" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A290" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="291" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A291" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="292" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A292" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="293" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A293" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="294" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A294" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="295" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A295" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="296" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A296" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="297" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A297" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="298" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A298" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="299" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A299" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="300" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A300" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="301" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A301" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="302" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A302" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="303" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A303" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="304" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A304" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="305" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A305" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="306" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A306" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="307" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A307" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="308" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A308" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="309" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A309" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="310" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A310" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="311" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A311" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="312" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A312" t="s">
+        <v>306</v>
       </c>
     </row>
   </sheetData>

--- a/исправления внести/эниология.xlsx
+++ b/исправления внести/эниология.xlsx
@@ -8,22 +8,34 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\исправления внести\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FF20D62-DBF8-466D-BE29-B670B7C0688D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63984390-3D0C-4847-A258-4765311E3593}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-10020" yWindow="2480" windowWidth="9500" windowHeight="10140" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-10020" yWindow="2480" windowWidth="9500" windowHeight="10140" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="после перевода" sheetId="2" r:id="rId1"/>
     <sheet name="простые" sheetId="3" r:id="rId2"/>
-    <sheet name="доперевод" sheetId="4" r:id="rId3"/>
+    <sheet name="ошибки в книге" sheetId="5" r:id="rId3"/>
+    <sheet name="доперевод" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">простые!$A$1:$A$338</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -33,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="292">
   <si>
     <t>структур</t>
   </si>
@@ -824,13 +836,91 @@
     <t>гранаты</t>
   </si>
   <si>
-    <t>фигурки</t>
-  </si>
-  <si>
     <t>психологи</t>
   </si>
   <si>
     <t>статуя</t>
+  </si>
+  <si>
+    <t>журналах</t>
+  </si>
+  <si>
+    <t>газетах</t>
+  </si>
+  <si>
+    <t>артиллерии</t>
+  </si>
+  <si>
+    <t>ракетных</t>
+  </si>
+  <si>
+    <t>фотоснимок</t>
+  </si>
+  <si>
+    <t>видеотелефону</t>
+  </si>
+  <si>
+    <t>определённое существующее действо</t>
+  </si>
+  <si>
+    <t>негэнтропию</t>
+  </si>
+  <si>
+    <t>номер</t>
+  </si>
+  <si>
+    <t>таблица</t>
+  </si>
+  <si>
+    <t>экономике</t>
+  </si>
+  <si>
+    <t>Библиотеку</t>
+  </si>
+  <si>
+    <t>энерговампиризмом</t>
+  </si>
+  <si>
+    <t>ушат холодной воды на голову,</t>
+  </si>
+  <si>
+    <t>ген</t>
+  </si>
+  <si>
+    <t>не нужен средство передвижения</t>
+  </si>
+  <si>
+    <t>рискуете</t>
+  </si>
+  <si>
+    <t>Телепортируетесь</t>
+  </si>
+  <si>
+    <t>прошла вездесущая изменение</t>
+  </si>
+  <si>
+    <t>формулу</t>
+  </si>
+  <si>
+    <t>а все находящиеся в зрители увидят</t>
+  </si>
+  <si>
+    <t>социуму</t>
+  </si>
+  <si>
+    <t>персонифицировать</t>
+  </si>
+  <si>
+    <t>конденсатора</t>
+  </si>
+  <si>
+    <t>диэлектрической проницаемости</t>
+  </si>
+  <si>
+    <t>прапорщик в вооружённые силы</t>
+  </si>
+  <si>
+    <t>кармический</t>
   </si>
 </sst>
 </file>
@@ -1174,7 +1264,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F21563D1-1294-476A-895B-8DF86C2F507F}">
-  <dimension ref="A2:A21"/>
+  <dimension ref="A2:A26"/>
   <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="23.08984375" customWidth="1"/>
@@ -1278,6 +1368,31 @@
     <row r="21" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A21" t="s">
         <v>258</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A22" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A23" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A24" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A25" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A26" t="s">
+        <v>290</v>
       </c>
     </row>
   </sheetData>
@@ -1323,11 +1438,6 @@
         <v>109</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.75">
-      <c r="A10" t="s">
-        <v>263</v>
-      </c>
-    </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
         <v>134</v>
@@ -1335,7 +1445,7 @@
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A12" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.75">
@@ -1358,6 +1468,11 @@
         <v>29</v>
       </c>
     </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A17" t="s">
+        <v>267</v>
+      </c>
+    </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A18" t="s">
         <v>81</v>
@@ -1378,6 +1493,21 @@
         <v>98</v>
       </c>
     </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A22" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A23" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A24" t="s">
+        <v>267</v>
+      </c>
+    </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A25" t="s">
         <v>131</v>
@@ -1388,16 +1518,36 @@
         <v>145</v>
       </c>
     </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A27" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A28" t="s">
+        <v>269</v>
+      </c>
+    </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A29" t="s">
         <v>68</v>
       </c>
     </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A30" t="s">
+        <v>270</v>
+      </c>
+    </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A31" t="s">
         <v>99</v>
       </c>
     </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A32" t="s">
+        <v>272</v>
+      </c>
+    </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A33" t="s">
         <v>127</v>
@@ -1408,6 +1558,16 @@
         <v>151</v>
       </c>
     </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A35" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A36" t="s">
+        <v>274</v>
+      </c>
+    </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A37" t="s">
         <v>159</v>
@@ -1423,6 +1583,11 @@
         <v>140</v>
       </c>
     </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A40" t="s">
+        <v>275</v>
+      </c>
+    </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A41" t="s">
         <v>36</v>
@@ -1458,6 +1623,16 @@
         <v>19</v>
       </c>
     </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A48" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A49" t="s">
+        <v>276</v>
+      </c>
+    </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A50" t="s">
         <v>138</v>
@@ -1493,6 +1668,16 @@
         <v>158</v>
       </c>
     </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A57" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A58" t="s">
+        <v>279</v>
+      </c>
+    </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A59" t="s">
         <v>143</v>
@@ -1528,6 +1713,11 @@
         <v>120</v>
       </c>
     </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A67" t="s">
+        <v>284</v>
+      </c>
+    </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A68" t="s">
         <v>146</v>
@@ -1538,6 +1728,11 @@
         <v>135</v>
       </c>
     </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A70" t="s">
+        <v>281</v>
+      </c>
+    </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A71" t="s">
         <v>112</v>
@@ -1548,6 +1743,21 @@
         <v>262</v>
       </c>
     </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A73" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A74" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A75" t="s">
+        <v>286</v>
+      </c>
+    </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A76" t="s">
         <v>83</v>
@@ -1558,6 +1768,11 @@
         <v>21</v>
       </c>
     </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A78" t="s">
+        <v>287</v>
+      </c>
+    </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A79" t="s">
         <v>93</v>
@@ -1583,6 +1798,11 @@
         <v>39</v>
       </c>
     </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A84" t="s">
+        <v>288</v>
+      </c>
+    </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A85" t="s">
         <v>142</v>
@@ -1591,6 +1811,21 @@
     <row r="86" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A86" t="s">
         <v>52</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A87" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A88" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A90" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.75">
@@ -2588,13 +2823,28 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4792E377-39EC-4785-9269-9C61E9BFD62D}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A1" t="s">
+        <v>278</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DBA598F-779B-4000-A874-2A5A01A11567}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
   </sheetData>

--- a/исправления внести/эниология.xlsx
+++ b/исправления внести/эниология.xlsx
@@ -1,25 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\исправления внести\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\исправления внести\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2ECF46A-E89B-41DF-B826-34E3D1C4FA7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{813A414B-0548-4CB9-875A-CB1ABC33E250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-12040" yWindow="400" windowWidth="10310" windowHeight="20690" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="после перевода" sheetId="2" r:id="rId1"/>
     <sheet name="простые" sheetId="3" r:id="rId2"/>
     <sheet name="ошибки в книге" sheetId="5" r:id="rId3"/>
     <sheet name="доперевод" sheetId="4" r:id="rId4"/>
+    <sheet name="составные" sheetId="6" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">простые!$A$1:$A$338</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">простые!$A$2:$B$211</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,12 +38,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="254">
   <si>
     <t>оперативная группа</t>
   </si>
@@ -155,9 +159,6 @@
     <t>мегагалактик</t>
   </si>
   <si>
-    <t>атомы</t>
-  </si>
-  <si>
     <t>протогалактики</t>
   </si>
   <si>
@@ -747,13 +748,73 @@
   </si>
   <si>
     <t>летоведения</t>
+  </si>
+  <si>
+    <t>планетарных систем.</t>
+  </si>
+  <si>
+    <t>микро</t>
+  </si>
+  <si>
+    <t>макро</t>
+  </si>
+  <si>
+    <t xml:space="preserve">кристаллической </t>
+  </si>
+  <si>
+    <t>молекулы</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Центр по исследованию</t>
+  </si>
+  <si>
+    <t>технократического </t>
+  </si>
+  <si>
+    <t xml:space="preserve">материализма </t>
+  </si>
+  <si>
+    <t>готическую зодчеств</t>
+  </si>
+  <si>
+    <t>бумеранг</t>
+  </si>
+  <si>
+    <t>энергетики</t>
+  </si>
+  <si>
+    <t xml:space="preserve">энергетических </t>
+  </si>
+  <si>
+    <t xml:space="preserve">спинирующих </t>
+  </si>
+  <si>
+    <t>тордионов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">спиновая </t>
+  </si>
+  <si>
+    <t>тахионов</t>
+  </si>
+  <si>
+    <t>сверхсветовых частиц</t>
+  </si>
+  <si>
+    <t xml:space="preserve">фотографировании </t>
+  </si>
+  <si>
+    <t xml:space="preserve">фотоэмульсии </t>
+  </si>
+  <si>
+    <t xml:space="preserve">спиновую </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -780,6 +841,10 @@
       <family val="1"/>
       <charset val="204"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <name val="LiberEmb"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -801,7 +866,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -810,6 +875,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1090,140 +1156,150 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F21563D1-1294-476A-895B-8DF86C2F507F}">
-  <dimension ref="A2:A27"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A2:A29"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="23.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1">
       <c r="A2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:1">
       <c r="A4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:1">
       <c r="A5" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:1">
       <c r="A13" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:1">
       <c r="A15" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
       <c r="A19" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
       <c r="A23" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>231</v>
+        <v>230</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>242</v>
       </c>
     </row>
   </sheetData>
@@ -1234,1065 +1310,1189 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F65167D-C510-40BD-B401-AA5A335D9CBB}">
   <dimension ref="A2:B278"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="29.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+        <v>232</v>
+      </c>
+      <c r="B16" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
       <c r="A18" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
       <c r="A23" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A50" s="3" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A55" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A56" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A57" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A58" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A59" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A60" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A61" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A62" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A63" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A64" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A65" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A66" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A67" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A68" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A69" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A70" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A71" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A72" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A73" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A74" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A75" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A77" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A78" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A80" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A81" t="s">
+    <row r="91" spans="1:1">
+      <c r="A91" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A82" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A83" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A84" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A85" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A86" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A87" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A88" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A89" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A90" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A91" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A92" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A93" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A94" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A95" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:1">
       <c r="A96" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.35">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
       <c r="A97" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.35">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
       <c r="A98" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:1">
       <c r="A99" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.35">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
       <c r="A100" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1">
+      <c r="A150" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1">
+      <c r="A153" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1">
+      <c r="A154" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1">
+      <c r="A156" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1">
+      <c r="A157" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1">
+      <c r="A159" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1">
+      <c r="A160" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1">
+      <c r="A161" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1">
+      <c r="A162" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1">
+      <c r="A163" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1">
+      <c r="A164" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1">
+      <c r="A165" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1">
+      <c r="A166" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1">
+      <c r="A167" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1">
+      <c r="A168" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1">
+      <c r="A169" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1">
+      <c r="A170" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1">
+      <c r="A171" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1">
+      <c r="A172" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1">
+      <c r="A173" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1">
+      <c r="A174" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1">
+      <c r="A175" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1">
+      <c r="A176" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1">
+      <c r="A177" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1">
+      <c r="A178" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1">
+      <c r="A179" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1">
+      <c r="A180" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1">
+      <c r="A181" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1">
+      <c r="A182" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1">
+      <c r="A183" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1">
+      <c r="A184" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1">
+      <c r="A185" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1">
+      <c r="A186" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1">
+      <c r="A187" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1">
+      <c r="A188" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1">
+      <c r="A189" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1">
+      <c r="A190" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1">
+      <c r="A191" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1">
+      <c r="A192" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1">
+      <c r="A193" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1">
+      <c r="A194" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1">
+      <c r="A195" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1">
+      <c r="A196" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1">
+      <c r="A197" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1">
+      <c r="A198" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1">
+      <c r="A199" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1">
+      <c r="A200" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1">
+      <c r="A201" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1">
+      <c r="A202" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1">
+      <c r="A203" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1">
+      <c r="A204" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1">
+      <c r="A205" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1">
+      <c r="A206" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1">
+      <c r="A207" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1">
+      <c r="A208" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A101" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A102" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A103" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A104" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A105" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A106" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A107" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A108" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A109" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A110" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A111" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A112" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A113" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A114" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A115" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A116" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A117" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A118" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A119" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A120" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A121" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A122" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A123" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A124" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A125" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A126" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A127" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A128" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A129" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A130" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A131" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A132" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A133" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A134" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A135" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A136" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A137" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A138" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A139" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A140" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A141" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A142" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A143" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A144" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A146" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A147" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A148" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A149" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A150" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A151" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A152" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A153" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A155" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A156" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A157" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A158" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A159" t="s">
+    <row r="209" spans="1:1">
+      <c r="A209" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1">
+      <c r="A210" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1">
+      <c r="A211" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1">
+      <c r="A212" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1">
+      <c r="A213" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1">
+      <c r="A214" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1">
+      <c r="A215" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1">
+      <c r="A216" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1" ht="17.5">
+      <c r="A217" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1">
+      <c r="A218" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1">
+      <c r="A219" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1">
+      <c r="A220" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1">
+      <c r="A221" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A160" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A161" t="s">
+    <row r="222" spans="1:1">
+      <c r="A222" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1">
+      <c r="A223" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1">
+      <c r="A224" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2">
+      <c r="A225" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2">
+      <c r="A226" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2">
+      <c r="A227" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A162" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A163" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A164" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A165" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A166" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A169" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A170" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A171" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A172" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A173" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A174" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A175" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A176" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A177" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A178" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A179" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A180" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A181" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A182" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A183" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A184" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A185" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A186" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A187" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A188" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A189" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A190" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A191" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A192" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A193" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A194" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A195" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A196" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A197" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A198" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A199" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A200" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A201" t="s">
-        <v>233</v>
-      </c>
-      <c r="B201" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A204" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A205" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A206" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A207" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A208" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="209" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A209" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="210" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A210" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="211" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A211" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="212" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A212" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="215" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A215" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="216" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A216" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="217" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A217" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="218" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A218" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="219" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A219" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="220" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A220" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="221" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A221" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="222" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A222" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="278" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:2">
+      <c r="A228" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2">
+      <c r="A229" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2">
+      <c r="A230" t="s">
+        <v>249</v>
+      </c>
+      <c r="B230" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2">
+      <c r="A231" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2">
+      <c r="A232" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2">
+      <c r="A233" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2">
+      <c r="A234" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="278" spans="1:1" ht="15.5">
       <c r="A278" s="2"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A282">
-    <sortCondition ref="A2:A282"/>
+  <autoFilter ref="A2:B211" xr:uid="{1F65167D-C510-40BD-B401-AA5A335D9CBB}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B278">
+    <sortCondition ref="A2:A278"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2302,11 +2502,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4792E377-39EC-4785-9269-9C61E9BFD62D}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
   </sheetData>
@@ -2317,11 +2517,29 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DBA598F-779B-4000-A874-2A5A01A11567}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>212</v>
+        <v>211</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B672A3D-6BD1-4167-A6FD-CFAEF2ED5EE0}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="20.08984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>234</v>
       </c>
     </row>
   </sheetData>

--- a/исправления внести/эниология.xlsx
+++ b/исправления внести/эниология.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\исправления внести\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Книги\переводчик_книг\исправления внести\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{813A414B-0548-4CB9-875A-CB1ABC33E250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C853DE0-18F9-43C2-A0CF-A9B54AF10D11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="2355" windowWidth="18315" windowHeight="11070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="после перевода" sheetId="2" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="331">
   <si>
     <t>оперативная группа</t>
   </si>
@@ -808,6 +808,237 @@
   </si>
   <si>
     <t xml:space="preserve">спиновую </t>
+  </si>
+  <si>
+    <t xml:space="preserve">материальности </t>
+  </si>
+  <si>
+    <t>нашу общество</t>
+  </si>
+  <si>
+    <t>наше общество</t>
+  </si>
+  <si>
+    <t>по создания необходимых</t>
+  </si>
+  <si>
+    <t>по созданию необхлдимых</t>
+  </si>
+  <si>
+    <t>полный количество</t>
+  </si>
+  <si>
+    <t>полное количество</t>
+  </si>
+  <si>
+    <t>весь савокупность</t>
+  </si>
+  <si>
+    <t>всю савокупность</t>
+  </si>
+  <si>
+    <t>какой правилом</t>
+  </si>
+  <si>
+    <t>каким правилам</t>
+  </si>
+  <si>
+    <t>наша земная общество</t>
+  </si>
+  <si>
+    <t>наше земное общество</t>
+  </si>
+  <si>
+    <t>тела будет безупречной</t>
+  </si>
+  <si>
+    <t>тела будет безупречным</t>
+  </si>
+  <si>
+    <t>нужная сведения</t>
+  </si>
+  <si>
+    <t>нужные сведения</t>
+  </si>
+  <si>
+    <t>могут быть записана</t>
+  </si>
+  <si>
+    <t>могут быть записаны</t>
+  </si>
+  <si>
+    <t>проявлениям сведениям</t>
+  </si>
+  <si>
+    <t>проявлениям сведений</t>
+  </si>
+  <si>
+    <t>никто на этой небесном</t>
+  </si>
+  <si>
+    <t>никто на этом небесномм</t>
+  </si>
+  <si>
+    <t>требуемую источники</t>
+  </si>
+  <si>
+    <t>требуемые источники</t>
+  </si>
+  <si>
+    <t>по такой же чертежу</t>
+  </si>
+  <si>
+    <t>по такому же чертежу</t>
+  </si>
+  <si>
+    <t>проходящих воин</t>
+  </si>
+  <si>
+    <t>проходящих воинов</t>
+  </si>
+  <si>
+    <t>на эту вопрос</t>
+  </si>
+  <si>
+    <t>на этот вопрос</t>
+  </si>
+  <si>
+    <t>такого связи</t>
+  </si>
+  <si>
+    <t>такой связи</t>
+  </si>
+  <si>
+    <t>из нашей применения</t>
+  </si>
+  <si>
+    <t>из нашего применения</t>
+  </si>
+  <si>
+    <t>первая мятеж</t>
+  </si>
+  <si>
+    <t>первый мятеж</t>
+  </si>
+  <si>
+    <t>вид власти не менялась</t>
+  </si>
+  <si>
+    <t>вид власти не менялся</t>
+  </si>
+  <si>
+    <t>российскому наледственности</t>
+  </si>
+  <si>
+    <t>сильнейшую повреждение</t>
+  </si>
+  <si>
+    <t>российской наследственности</t>
+  </si>
+  <si>
+    <t>сильнейшее повреждение</t>
+  </si>
+  <si>
+    <t>нашей планетарной общества</t>
+  </si>
+  <si>
+    <t>нашего планетарного общества</t>
+  </si>
+  <si>
+    <t>природный сырье</t>
+  </si>
+  <si>
+    <t>природное сырье</t>
+  </si>
+  <si>
+    <t>нашу небесную телу</t>
+  </si>
+  <si>
+    <t>наше небесное тело</t>
+  </si>
+  <si>
+    <t>неизвестную сведения</t>
+  </si>
+  <si>
+    <t>неизвестные сведения</t>
+  </si>
+  <si>
+    <t>книжного письменности</t>
+  </si>
+  <si>
+    <t>книжной письменности</t>
+  </si>
+  <si>
+    <t>письменной устройством</t>
+  </si>
+  <si>
+    <t>птсьменным устройством</t>
+  </si>
+  <si>
+    <t>наследсвенной сведениям</t>
+  </si>
+  <si>
+    <t>неследственных сведений</t>
+  </si>
+  <si>
+    <t>страшного зараза</t>
+  </si>
+  <si>
+    <t>страшной заразы</t>
+  </si>
+  <si>
+    <t>вашей небесного</t>
+  </si>
+  <si>
+    <t>вашего небесного</t>
+  </si>
+  <si>
+    <t>пршедшим преграда</t>
+  </si>
+  <si>
+    <t>прошедшим преграду</t>
+  </si>
+  <si>
+    <t>по всей небесном теле</t>
+  </si>
+  <si>
+    <t>по всему небесному телу</t>
+  </si>
+  <si>
+    <t>всей земного</t>
+  </si>
+  <si>
+    <t>всего земного</t>
+  </si>
+  <si>
+    <t>на всеобщем обстановке</t>
+  </si>
+  <si>
+    <t>на всеобщей обстановке</t>
+  </si>
+  <si>
+    <t xml:space="preserve">в ход земной </t>
+  </si>
+  <si>
+    <t>в ходе земного</t>
+  </si>
+  <si>
+    <t>железнодорожная стихийное</t>
+  </si>
+  <si>
+    <t>железнодорожное стихийное</t>
+  </si>
+  <si>
+    <t>изменилась при</t>
+  </si>
+  <si>
+    <t>изменился при</t>
+  </si>
+  <si>
+    <t>в этой устройстве</t>
+  </si>
+  <si>
+    <t>в этом устройстве</t>
   </si>
 </sst>
 </file>
@@ -1156,10 +1387,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F21563D1-1294-476A-895B-8DF86C2F507F}">
-  <dimension ref="A2:A29"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="A2:C67"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.08984375" customWidth="1"/>
+    <col min="1" max="1" width="27.28515625" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" customWidth="1"/>
+    <col min="3" max="3" width="33" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:1">
@@ -1237,69 +1470,373 @@
         <v>192</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" spans="1:3">
       <c r="A21" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:3">
       <c r="A22" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:3">
       <c r="A23" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:3">
       <c r="A24" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:3">
       <c r="A25" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:3">
       <c r="A26" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" spans="1:3">
       <c r="A27" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" spans="1:3">
       <c r="A28" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
+    <row r="29" spans="1:3">
       <c r="A29" t="s">
         <v>242</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>255</v>
+      </c>
+      <c r="C30" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
+        <v>257</v>
+      </c>
+      <c r="C31" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>259</v>
+      </c>
+      <c r="C32" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>261</v>
+      </c>
+      <c r="C33" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>263</v>
+      </c>
+      <c r="C34" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
+        <v>265</v>
+      </c>
+      <c r="C35" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
+        <v>267</v>
+      </c>
+      <c r="C36" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
+        <v>269</v>
+      </c>
+      <c r="C37" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" t="s">
+        <v>271</v>
+      </c>
+      <c r="C38" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" t="s">
+        <v>273</v>
+      </c>
+      <c r="C39" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" t="s">
+        <v>275</v>
+      </c>
+      <c r="C40" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" t="s">
+        <v>277</v>
+      </c>
+      <c r="C41" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" t="s">
+        <v>279</v>
+      </c>
+      <c r="C42" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" t="s">
+        <v>281</v>
+      </c>
+      <c r="C43" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" t="s">
+        <v>283</v>
+      </c>
+      <c r="C44" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" t="s">
+        <v>285</v>
+      </c>
+      <c r="C45" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" t="s">
+        <v>287</v>
+      </c>
+      <c r="C46" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" t="s">
+        <v>289</v>
+      </c>
+      <c r="C47" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" t="s">
+        <v>291</v>
+      </c>
+      <c r="C48" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" t="s">
+        <v>293</v>
+      </c>
+      <c r="C49" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" t="s">
+        <v>294</v>
+      </c>
+      <c r="C50" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" t="s">
+        <v>297</v>
+      </c>
+      <c r="C51" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" t="s">
+        <v>299</v>
+      </c>
+      <c r="C52" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" t="s">
+        <v>301</v>
+      </c>
+      <c r="C53" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" t="s">
+        <v>303</v>
+      </c>
+      <c r="C54" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" t="s">
+        <v>305</v>
+      </c>
+      <c r="C55" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" t="s">
+        <v>307</v>
+      </c>
+      <c r="C56" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" t="s">
+        <v>309</v>
+      </c>
+      <c r="C57" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" t="s">
+        <v>311</v>
+      </c>
+      <c r="C58" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" t="s">
+        <v>313</v>
+      </c>
+      <c r="C59" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" t="s">
+        <v>315</v>
+      </c>
+      <c r="C60" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" t="s">
+        <v>317</v>
+      </c>
+      <c r="C61" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" t="s">
+        <v>319</v>
+      </c>
+      <c r="C62" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" t="s">
+        <v>321</v>
+      </c>
+      <c r="C63" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" t="s">
+        <v>323</v>
+      </c>
+      <c r="C64" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" t="s">
+        <v>325</v>
+      </c>
+      <c r="C65" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" t="s">
+        <v>327</v>
+      </c>
+      <c r="C66" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" t="s">
+        <v>329</v>
+      </c>
+      <c r="C67" t="s">
+        <v>330</v>
       </c>
     </row>
   </sheetData>
@@ -1310,9 +1847,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F65167D-C510-40BD-B401-AA5A335D9CBB}">
   <dimension ref="A2:B278"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="29.26953125" customWidth="1"/>
+    <col min="1" max="1" width="29.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:2">
@@ -2393,7 +2930,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="217" spans="1:1" ht="17.5">
+    <row r="217" spans="1:1" ht="18">
       <c r="A217" s="4" t="s">
         <v>240</v>
       </c>
@@ -2486,7 +3023,12 @@
         <v>253</v>
       </c>
     </row>
-    <row r="278" spans="1:1" ht="15.5">
+    <row r="235" spans="1:2">
+      <c r="A235" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="278" spans="1:1" ht="15.75">
       <c r="A278" s="2"/>
     </row>
   </sheetData>
@@ -2502,7 +3044,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4792E377-39EC-4785-9269-9C61E9BFD62D}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
@@ -2517,7 +3059,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DBA598F-779B-4000-A874-2A5A01A11567}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
@@ -2532,9 +3074,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B672A3D-6BD1-4167-A6FD-CFAEF2ED5EE0}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="20.08984375" customWidth="1"/>
+    <col min="1" max="1" width="20.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">

--- a/исправления внести/эниология.xlsx
+++ b/исправления внести/эниология.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Книги\переводчик_книг\исправления внести\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\исправления внести\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C853DE0-18F9-43C2-A0CF-A9B54AF10D11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3C4966B-B8D9-4232-A586-17C7C120553F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2355" windowWidth="18315" windowHeight="11070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="15585" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="после перевода" sheetId="2" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="235">
   <si>
     <t>оперативная группа</t>
   </si>
@@ -489,27 +489,9 @@
     <t>кармических</t>
   </si>
   <si>
-    <t>духовный наставник</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> следовать кадры</t>
-  </si>
-  <si>
-    <t>колдовства белой или черной.</t>
-  </si>
-  <si>
-    <t>Уровень духовной колдовства</t>
-  </si>
-  <si>
     <t>энергетики,</t>
   </si>
   <si>
-    <t>коммуникаций</t>
-  </si>
-  <si>
-    <t>гуру</t>
-  </si>
-  <si>
     <t>компании</t>
   </si>
   <si>
@@ -546,9 +528,6 @@
     <t>энергоцентр</t>
   </si>
   <si>
-    <t>подвыпившая предприятие</t>
-  </si>
-  <si>
     <t>импотенция</t>
   </si>
   <si>
@@ -558,9 +537,6 @@
     <t>иммунной</t>
   </si>
   <si>
-    <t>географический меридиан</t>
-  </si>
-  <si>
     <t>энергоинформационные меридианы</t>
   </si>
   <si>
@@ -624,12 +600,6 @@
     <t>энергоинформационный возможность</t>
   </si>
   <si>
-    <t>получаемой сведениям</t>
-  </si>
-  <si>
-    <t>информационную составляющую</t>
-  </si>
-  <si>
     <t>эмоционально-психотронные установки</t>
   </si>
   <si>
@@ -648,9 +618,6 @@
     <t>кодировщика</t>
   </si>
   <si>
-    <t>Новошахтинской научно-исследовательской исследовательские отделы</t>
-  </si>
-  <si>
     <t>телепатического</t>
   </si>
   <si>
@@ -660,15 +627,6 @@
     <t>дискета</t>
   </si>
   <si>
-    <t>Этот книгопечатный “произведение искусства”</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Правило действия подобных мыслеобразов вполне понятен </t>
-  </si>
-  <si>
-    <t>психотронные виде поведения</t>
-  </si>
-  <si>
     <t>визуализировать</t>
   </si>
   <si>
@@ -702,9 +660,6 @@
     <t>видеотелефону</t>
   </si>
   <si>
-    <t>определённое существующее действо</t>
-  </si>
-  <si>
     <t>негэнтропию</t>
   </si>
   <si>
@@ -720,27 +675,12 @@
     <t>ген</t>
   </si>
   <si>
-    <t>не нужен средство передвижения</t>
-  </si>
-  <si>
-    <t>прошла вездесущая изменение</t>
-  </si>
-  <si>
-    <t>а все находящиеся в зрители увидят</t>
-  </si>
-  <si>
     <t>персонифицировать</t>
   </si>
   <si>
-    <t>прапорщик в вооружённые силы</t>
-  </si>
-  <si>
     <t>сферой?</t>
   </si>
   <si>
-    <t>многомерного живой особи,</t>
-  </si>
-  <si>
     <t>энергоинформационных полях</t>
   </si>
   <si>
@@ -765,18 +705,12 @@
     <t>молекулы</t>
   </si>
   <si>
-    <t xml:space="preserve"> Центр по исследованию</t>
-  </si>
-  <si>
     <t>технократического </t>
   </si>
   <si>
     <t xml:space="preserve">материализма </t>
   </si>
   <si>
-    <t>готическую зодчеств</t>
-  </si>
-  <si>
     <t>бумеранг</t>
   </si>
   <si>
@@ -813,232 +747,10 @@
     <t xml:space="preserve">материальности </t>
   </si>
   <si>
-    <t>нашу общество</t>
-  </si>
-  <si>
-    <t>наше общество</t>
-  </si>
-  <si>
-    <t>по создания необходимых</t>
-  </si>
-  <si>
-    <t>по созданию необхлдимых</t>
-  </si>
-  <si>
-    <t>полный количество</t>
-  </si>
-  <si>
-    <t>полное количество</t>
-  </si>
-  <si>
-    <t>весь савокупность</t>
-  </si>
-  <si>
-    <t>всю савокупность</t>
-  </si>
-  <si>
-    <t>какой правилом</t>
-  </si>
-  <si>
-    <t>каким правилам</t>
-  </si>
-  <si>
-    <t>наша земная общество</t>
-  </si>
-  <si>
-    <t>наше земное общество</t>
-  </si>
-  <si>
-    <t>тела будет безупречной</t>
-  </si>
-  <si>
-    <t>тела будет безупречным</t>
-  </si>
-  <si>
-    <t>нужная сведения</t>
-  </si>
-  <si>
-    <t>нужные сведения</t>
-  </si>
-  <si>
-    <t>могут быть записана</t>
-  </si>
-  <si>
-    <t>могут быть записаны</t>
-  </si>
-  <si>
-    <t>проявлениям сведениям</t>
-  </si>
-  <si>
-    <t>проявлениям сведений</t>
-  </si>
-  <si>
-    <t>никто на этой небесном</t>
-  </si>
-  <si>
-    <t>никто на этом небесномм</t>
-  </si>
-  <si>
-    <t>требуемую источники</t>
-  </si>
-  <si>
-    <t>требуемые источники</t>
-  </si>
-  <si>
-    <t>по такой же чертежу</t>
-  </si>
-  <si>
-    <t>по такому же чертежу</t>
-  </si>
-  <si>
-    <t>проходящих воин</t>
-  </si>
-  <si>
-    <t>проходящих воинов</t>
-  </si>
-  <si>
-    <t>на эту вопрос</t>
-  </si>
-  <si>
-    <t>на этот вопрос</t>
-  </si>
-  <si>
-    <t>такого связи</t>
-  </si>
-  <si>
-    <t>такой связи</t>
-  </si>
-  <si>
-    <t>из нашей применения</t>
-  </si>
-  <si>
-    <t>из нашего применения</t>
-  </si>
-  <si>
-    <t>первая мятеж</t>
-  </si>
-  <si>
-    <t>первый мятеж</t>
-  </si>
-  <si>
-    <t>вид власти не менялась</t>
-  </si>
-  <si>
-    <t>вид власти не менялся</t>
-  </si>
-  <si>
-    <t>российскому наледственности</t>
-  </si>
-  <si>
-    <t>сильнейшую повреждение</t>
-  </si>
-  <si>
-    <t>российской наследственности</t>
-  </si>
-  <si>
-    <t>сильнейшее повреждение</t>
-  </si>
-  <si>
-    <t>нашей планетарной общества</t>
-  </si>
-  <si>
-    <t>нашего планетарного общества</t>
-  </si>
-  <si>
-    <t>природный сырье</t>
-  </si>
-  <si>
-    <t>природное сырье</t>
-  </si>
-  <si>
-    <t>нашу небесную телу</t>
-  </si>
-  <si>
-    <t>наше небесное тело</t>
-  </si>
-  <si>
-    <t>неизвестную сведения</t>
-  </si>
-  <si>
-    <t>неизвестные сведения</t>
-  </si>
-  <si>
-    <t>книжного письменности</t>
-  </si>
-  <si>
-    <t>книжной письменности</t>
-  </si>
-  <si>
-    <t>письменной устройством</t>
-  </si>
-  <si>
-    <t>птсьменным устройством</t>
-  </si>
-  <si>
-    <t>наследсвенной сведениям</t>
-  </si>
-  <si>
-    <t>неследственных сведений</t>
-  </si>
-  <si>
-    <t>страшного зараза</t>
-  </si>
-  <si>
-    <t>страшной заразы</t>
-  </si>
-  <si>
-    <t>вашей небесного</t>
-  </si>
-  <si>
-    <t>вашего небесного</t>
-  </si>
-  <si>
-    <t>пршедшим преграда</t>
-  </si>
-  <si>
-    <t>прошедшим преграду</t>
-  </si>
-  <si>
-    <t>по всей небесном теле</t>
-  </si>
-  <si>
-    <t>по всему небесному телу</t>
-  </si>
-  <si>
-    <t>всей земного</t>
-  </si>
-  <si>
-    <t>всего земного</t>
-  </si>
-  <si>
-    <t>на всеобщем обстановке</t>
-  </si>
-  <si>
-    <t>на всеобщей обстановке</t>
-  </si>
-  <si>
-    <t xml:space="preserve">в ход земной </t>
-  </si>
-  <si>
-    <t>в ходе земного</t>
-  </si>
-  <si>
-    <t>железнодорожная стихийное</t>
-  </si>
-  <si>
-    <t>железнодорожное стихийное</t>
-  </si>
-  <si>
     <t>изменилась при</t>
   </si>
   <si>
     <t>изменился при</t>
-  </si>
-  <si>
-    <t>в этой устройстве</t>
-  </si>
-  <si>
-    <t>в этом устройстве</t>
   </si>
 </sst>
 </file>
@@ -1387,10 +1099,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F21563D1-1294-476A-895B-8DF86C2F507F}">
-  <dimension ref="A2:C67"/>
+  <dimension ref="A2:C41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="27.28515625" customWidth="1"/>
+    <col min="1" max="1" width="43" customWidth="1"/>
     <col min="2" max="2" width="14.42578125" customWidth="1"/>
     <col min="3" max="3" width="33" customWidth="1"/>
   </cols>
@@ -1400,443 +1112,37 @@
         <v>146</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
-      <c r="A3" t="s">
-        <v>147</v>
-      </c>
-    </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>150</v>
-      </c>
-    </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" t="s">
-        <v>255</v>
-      </c>
-      <c r="C30" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" t="s">
-        <v>257</v>
-      </c>
-      <c r="C31" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" t="s">
-        <v>259</v>
-      </c>
-      <c r="C32" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" t="s">
-        <v>261</v>
-      </c>
-      <c r="C33" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" t="s">
-        <v>263</v>
-      </c>
-      <c r="C34" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" t="s">
-        <v>265</v>
-      </c>
-      <c r="C35" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" t="s">
-        <v>267</v>
-      </c>
-      <c r="C36" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" t="s">
-        <v>269</v>
-      </c>
-      <c r="C37" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" t="s">
-        <v>271</v>
-      </c>
-      <c r="C38" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" t="s">
-        <v>273</v>
-      </c>
-      <c r="C39" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" t="s">
-        <v>275</v>
-      </c>
-      <c r="C40" t="s">
-        <v>276</v>
+        <v>183</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>277</v>
+        <v>233</v>
       </c>
       <c r="C41" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" t="s">
-        <v>279</v>
-      </c>
-      <c r="C42" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" t="s">
-        <v>281</v>
-      </c>
-      <c r="C43" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" t="s">
-        <v>283</v>
-      </c>
-      <c r="C44" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" t="s">
-        <v>285</v>
-      </c>
-      <c r="C45" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46" t="s">
-        <v>287</v>
-      </c>
-      <c r="C46" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="A47" t="s">
-        <v>289</v>
-      </c>
-      <c r="C47" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" t="s">
-        <v>291</v>
-      </c>
-      <c r="C48" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" t="s">
-        <v>293</v>
-      </c>
-      <c r="C49" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50" t="s">
-        <v>294</v>
-      </c>
-      <c r="C50" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51" t="s">
-        <v>297</v>
-      </c>
-      <c r="C51" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52" t="s">
-        <v>299</v>
-      </c>
-      <c r="C52" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3">
-      <c r="A53" t="s">
-        <v>301</v>
-      </c>
-      <c r="C53" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3">
-      <c r="A54" t="s">
-        <v>303</v>
-      </c>
-      <c r="C54" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3">
-      <c r="A55" t="s">
-        <v>305</v>
-      </c>
-      <c r="C55" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3">
-      <c r="A56" t="s">
-        <v>307</v>
-      </c>
-      <c r="C56" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3">
-      <c r="A57" t="s">
-        <v>309</v>
-      </c>
-      <c r="C57" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3">
-      <c r="A58" t="s">
-        <v>311</v>
-      </c>
-      <c r="C58" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3">
-      <c r="A59" t="s">
-        <v>313</v>
-      </c>
-      <c r="C59" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3">
-      <c r="A60" t="s">
-        <v>315</v>
-      </c>
-      <c r="C60" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3">
-      <c r="A61" t="s">
-        <v>317</v>
-      </c>
-      <c r="C61" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3">
-      <c r="A62" t="s">
-        <v>319</v>
-      </c>
-      <c r="C62" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3">
-      <c r="A63" t="s">
-        <v>321</v>
-      </c>
-      <c r="C63" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3">
-      <c r="A64" t="s">
-        <v>323</v>
-      </c>
-      <c r="C64" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3">
-      <c r="A65" t="s">
-        <v>325</v>
-      </c>
-      <c r="C65" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3">
-      <c r="A66" t="s">
-        <v>327</v>
-      </c>
-      <c r="C66" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3">
-      <c r="A67" t="s">
-        <v>329</v>
-      </c>
-      <c r="C67" t="s">
-        <v>330</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -1894,12 +1200,12 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1914,7 +1220,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1924,15 +1230,15 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>232</v>
+        <v>212</v>
       </c>
       <c r="B16" t="s">
-        <v>233</v>
+        <v>213</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>220</v>
+        <v>205</v>
       </c>
     </row>
     <row r="18" spans="1:1">
@@ -1977,12 +1283,12 @@
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
     </row>
     <row r="28" spans="1:1">
@@ -1992,12 +1298,12 @@
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
     </row>
     <row r="31" spans="1:1">
@@ -2012,12 +1318,12 @@
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
     </row>
     <row r="35" spans="1:1">
@@ -2032,7 +1338,7 @@
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
     </row>
     <row r="38" spans="1:1">
@@ -2042,7 +1348,7 @@
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
     </row>
     <row r="40" spans="1:1">
@@ -2052,17 +1358,17 @@
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
     </row>
     <row r="44" spans="1:1">
@@ -2092,12 +1398,12 @@
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="3" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
     </row>
     <row r="51" spans="1:1">
@@ -2127,7 +1433,7 @@
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
     </row>
     <row r="57" spans="1:1">
@@ -2137,7 +1443,7 @@
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
     </row>
     <row r="59" spans="1:1">
@@ -2182,7 +1488,7 @@
     </row>
     <row r="67" spans="1:1">
       <c r="A67" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
     </row>
     <row r="68" spans="1:1">
@@ -2207,7 +1513,7 @@
     </row>
     <row r="72" spans="1:1">
       <c r="A72" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
     </row>
     <row r="73" spans="1:1">
@@ -2217,7 +1523,7 @@
     </row>
     <row r="74" spans="1:1">
       <c r="A74" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
     </row>
     <row r="75" spans="1:1">
@@ -2252,7 +1558,7 @@
     </row>
     <row r="81" spans="1:1">
       <c r="A81" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
     </row>
     <row r="82" spans="1:1">
@@ -2307,12 +1613,12 @@
     </row>
     <row r="92" spans="1:1">
       <c r="A92" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="94" spans="1:1">
@@ -2357,12 +1663,12 @@
     </row>
     <row r="102" spans="1:1">
       <c r="A102" t="s">
-        <v>219</v>
+        <v>204</v>
       </c>
     </row>
     <row r="103" spans="1:1">
       <c r="A103" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
     </row>
     <row r="104" spans="1:1">
@@ -2372,12 +1678,12 @@
     </row>
     <row r="105" spans="1:1">
       <c r="A105" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
     </row>
     <row r="106" spans="1:1">
       <c r="A106" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
     </row>
     <row r="107" spans="1:1">
@@ -2387,7 +1693,7 @@
     </row>
     <row r="108" spans="1:1">
       <c r="A108" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
     </row>
     <row r="109" spans="1:1">
@@ -2447,7 +1753,7 @@
     </row>
     <row r="120" spans="1:1">
       <c r="A120" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
     </row>
     <row r="121" spans="1:1">
@@ -2472,7 +1778,7 @@
     </row>
     <row r="125" spans="1:1">
       <c r="A125" t="s">
-        <v>227</v>
+        <v>209</v>
       </c>
     </row>
     <row r="126" spans="1:1">
@@ -2497,7 +1803,7 @@
     </row>
     <row r="130" spans="1:1">
       <c r="A130" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="131" spans="1:1">
@@ -2512,7 +1818,7 @@
     </row>
     <row r="133" spans="1:1">
       <c r="A133" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
     </row>
     <row r="134" spans="1:1">
@@ -2532,12 +1838,12 @@
     </row>
     <row r="137" spans="1:1">
       <c r="A137" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
     </row>
     <row r="138" spans="1:1">
       <c r="A138" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
     </row>
     <row r="139" spans="1:1">
@@ -2552,12 +1858,12 @@
     </row>
     <row r="141" spans="1:1">
       <c r="A141" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
     </row>
     <row r="142" spans="1:1">
       <c r="A142" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
     </row>
     <row r="143" spans="1:1">
@@ -2567,7 +1873,7 @@
     </row>
     <row r="144" spans="1:1">
       <c r="A144" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
     </row>
     <row r="145" spans="1:1">
@@ -2587,12 +1893,12 @@
     </row>
     <row r="148" spans="1:1">
       <c r="A148" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
     </row>
     <row r="149" spans="1:1">
       <c r="A149" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
     </row>
     <row r="150" spans="1:1">
@@ -2602,7 +1908,7 @@
     </row>
     <row r="151" spans="1:1">
       <c r="A151" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="152" spans="1:1">
@@ -2637,7 +1943,7 @@
     </row>
     <row r="158" spans="1:1">
       <c r="A158" t="s">
-        <v>229</v>
+        <v>210</v>
       </c>
     </row>
     <row r="159" spans="1:1">
@@ -2652,12 +1958,12 @@
     </row>
     <row r="161" spans="1:1">
       <c r="A161" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
     </row>
     <row r="162" spans="1:1">
       <c r="A162" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
     </row>
     <row r="163" spans="1:1">
@@ -2687,22 +1993,22 @@
     </row>
     <row r="168" spans="1:1">
       <c r="A168" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
     </row>
     <row r="169" spans="1:1">
       <c r="A169" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
     </row>
     <row r="170" spans="1:1">
       <c r="A170" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
     </row>
     <row r="171" spans="1:1">
       <c r="A171" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
     </row>
     <row r="172" spans="1:1">
@@ -2727,7 +2033,7 @@
     </row>
     <row r="176" spans="1:1">
       <c r="A176" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
     </row>
     <row r="177" spans="1:1">
@@ -2782,7 +2088,7 @@
     </row>
     <row r="187" spans="1:1">
       <c r="A187" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
     </row>
     <row r="188" spans="1:1">
@@ -2837,7 +2143,7 @@
     </row>
     <row r="198" spans="1:1">
       <c r="A198" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
     </row>
     <row r="199" spans="1:1">
@@ -2847,7 +2153,7 @@
     </row>
     <row r="200" spans="1:1">
       <c r="A200" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
     </row>
     <row r="201" spans="1:1">
@@ -2862,7 +2168,7 @@
     </row>
     <row r="203" spans="1:1">
       <c r="A203" t="s">
-        <v>221</v>
+        <v>206</v>
       </c>
     </row>
     <row r="204" spans="1:1">
@@ -2872,17 +2178,17 @@
     </row>
     <row r="205" spans="1:1">
       <c r="A205" t="s">
-        <v>231</v>
+        <v>211</v>
       </c>
     </row>
     <row r="206" spans="1:1">
       <c r="A206" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
     </row>
     <row r="207" spans="1:1">
       <c r="A207" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
     </row>
     <row r="208" spans="1:1">
@@ -2892,12 +2198,12 @@
     </row>
     <row r="209" spans="1:1">
       <c r="A209" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
     </row>
     <row r="210" spans="1:1">
       <c r="A210" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
     </row>
     <row r="211" spans="1:1">
@@ -2912,32 +2218,32 @@
     </row>
     <row r="213" spans="1:1">
       <c r="A213" t="s">
-        <v>235</v>
+        <v>215</v>
       </c>
     </row>
     <row r="214" spans="1:1">
       <c r="A214" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
     </row>
     <row r="215" spans="1:1">
       <c r="A215" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
     </row>
     <row r="216" spans="1:1">
       <c r="A216" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
     </row>
     <row r="217" spans="1:1" ht="18">
       <c r="A217" s="4" t="s">
-        <v>240</v>
+        <v>219</v>
       </c>
     </row>
     <row r="218" spans="1:1">
       <c r="A218" t="s">
-        <v>241</v>
+        <v>220</v>
       </c>
     </row>
     <row r="219" spans="1:1">
@@ -2947,7 +2253,7 @@
     </row>
     <row r="220" spans="1:1">
       <c r="A220" t="s">
-        <v>243</v>
+        <v>221</v>
       </c>
     </row>
     <row r="221" spans="1:1">
@@ -2957,22 +2263,22 @@
     </row>
     <row r="222" spans="1:1">
       <c r="A222" t="s">
-        <v>244</v>
+        <v>222</v>
       </c>
     </row>
     <row r="223" spans="1:1">
       <c r="A223" t="s">
-        <v>245</v>
+        <v>223</v>
       </c>
     </row>
     <row r="224" spans="1:1">
       <c r="A224" t="s">
-        <v>246</v>
+        <v>224</v>
       </c>
     </row>
     <row r="225" spans="1:2">
       <c r="A225" t="s">
-        <v>247</v>
+        <v>225</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -2992,15 +2298,15 @@
     </row>
     <row r="229" spans="1:2">
       <c r="A229" t="s">
-        <v>248</v>
+        <v>226</v>
       </c>
     </row>
     <row r="230" spans="1:2">
       <c r="A230" t="s">
-        <v>249</v>
+        <v>227</v>
       </c>
       <c r="B230" t="s">
-        <v>250</v>
+        <v>228</v>
       </c>
     </row>
     <row r="231" spans="1:2">
@@ -3010,22 +2316,22 @@
     </row>
     <row r="232" spans="1:2">
       <c r="A232" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
     </row>
     <row r="233" spans="1:2">
       <c r="A233" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
     </row>
     <row r="234" spans="1:2">
       <c r="A234" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
     </row>
     <row r="235" spans="1:2">
       <c r="A235" t="s">
-        <v>254</v>
+        <v>232</v>
       </c>
     </row>
     <row r="278" spans="1:1" ht="15.75">
@@ -3048,7 +2354,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -3063,7 +2369,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -3081,7 +2387,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>234</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>

--- a/исправления внести/эниология.xlsx
+++ b/исправления внести/эниология.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\исправления внести\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\исправления внести\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3C4966B-B8D9-4232-A586-17C7C120553F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DD8FC9E-9DA8-4133-8543-9671E1EDE223}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="15585" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25510" yWindow="0" windowWidth="12980" windowHeight="20970" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="после перевода" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="составные" sheetId="6" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">простые!$A$2:$B$211</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">простые!$A$2:$B$278</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,25 +38,16 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="197">
   <si>
     <t>оперативная группа</t>
   </si>
   <si>
-    <t>физическое</t>
-  </si>
-  <si>
-    <t>Информационных Полях,</t>
-  </si>
-  <si>
     <t>энвольтирования</t>
   </si>
   <si>
@@ -69,9 +60,6 @@
     <t>онкология…</t>
   </si>
   <si>
-    <t>физическая</t>
-  </si>
-  <si>
     <t>«фантиками»,</t>
   </si>
   <si>
@@ -84,9 +72,6 @@
     <t>физической.</t>
   </si>
   <si>
-    <t>информационное</t>
-  </si>
-  <si>
     <t>энергетических</t>
   </si>
   <si>
@@ -102,9 +87,6 @@
     <t>энергетики.</t>
   </si>
   <si>
-    <t>ориентации</t>
-  </si>
-  <si>
     <t>биолазера:</t>
   </si>
   <si>
@@ -150,21 +132,12 @@
     <t>академиком</t>
   </si>
   <si>
-    <t>материализма</t>
-  </si>
-  <si>
-    <t>объемную</t>
-  </si>
-  <si>
     <t>мегагалактик</t>
   </si>
   <si>
     <t>протогалактики</t>
   </si>
   <si>
-    <t>массы</t>
-  </si>
-  <si>
     <t>молитвой</t>
   </si>
   <si>
@@ -177,12 +150,6 @@
     <t>полированного</t>
   </si>
   <si>
-    <t>фонового</t>
-  </si>
-  <si>
-    <t>изотропной</t>
-  </si>
-  <si>
     <t>нейтрино</t>
   </si>
   <si>
@@ -198,9 +165,6 @@
     <t>электронные</t>
   </si>
   <si>
-    <t>информационной</t>
-  </si>
-  <si>
     <t>центр по исследованию</t>
   </si>
   <si>
@@ -213,9 +177,6 @@
     <t>технократический</t>
   </si>
   <si>
-    <t>метакодов</t>
-  </si>
-  <si>
     <t>биороботов</t>
   </si>
   <si>
@@ -225,9 +186,6 @@
     <t>литературных</t>
   </si>
   <si>
-    <t>сугубо</t>
-  </si>
-  <si>
     <t>фотопечати</t>
   </si>
   <si>
@@ -240,18 +198,12 @@
     <t>сенсорика</t>
   </si>
   <si>
-    <t>многократно</t>
-  </si>
-  <si>
     <t>микролептонных</t>
   </si>
   <si>
     <t>тахионных</t>
   </si>
   <si>
-    <t>массой</t>
-  </si>
-  <si>
     <t>спинторсионных</t>
   </si>
   <si>
@@ -261,9 +213,6 @@
     <t>спиновая</t>
   </si>
   <si>
-    <t>вакуума</t>
-  </si>
-  <si>
     <t>голографии</t>
   </si>
   <si>
@@ -276,9 +225,6 @@
     <t>фотографируемого</t>
   </si>
   <si>
-    <t>ориентацию</t>
-  </si>
-  <si>
     <t>эмульсии</t>
   </si>
   <si>
@@ -297,9 +243,6 @@
     <t>алгоритму</t>
   </si>
   <si>
-    <t>контейнере</t>
-  </si>
-  <si>
     <t>пермалоевом</t>
   </si>
   <si>
@@ -312,9 +255,6 @@
     <t>паралогических</t>
   </si>
   <si>
-    <t>метрики</t>
-  </si>
-  <si>
     <t>переориентировать</t>
   </si>
   <si>
@@ -327,9 +267,6 @@
     <t>полимеры</t>
   </si>
   <si>
-    <t>молекула</t>
-  </si>
-  <si>
     <t>мономолекулы</t>
   </si>
   <si>
@@ -351,15 +288,9 @@
     <t>гексамеров</t>
   </si>
   <si>
-    <t>схема</t>
-  </si>
-  <si>
     <t>ассоциативов</t>
   </si>
   <si>
-    <t>ориентируемую</t>
-  </si>
-  <si>
     <t>перекодирование</t>
   </si>
   <si>
@@ -384,15 +315,9 @@
     <t>комонента</t>
   </si>
   <si>
-    <t>объемнорезонирующих</t>
-  </si>
-  <si>
     <t>фотоаппарат</t>
   </si>
   <si>
-    <t>инкарционного</t>
-  </si>
-  <si>
     <t>диаорни</t>
   </si>
   <si>
@@ -438,21 +363,12 @@
     <t>вертикали</t>
   </si>
   <si>
-    <t>фоне</t>
-  </si>
-  <si>
     <t>сенсорика,</t>
   </si>
   <si>
-    <t>вакуума»</t>
-  </si>
-  <si>
     <t>миллиграмма</t>
   </si>
   <si>
-    <t>метриках</t>
-  </si>
-  <si>
     <t>«биопотенцеры»</t>
   </si>
   <si>
@@ -498,9 +414,6 @@
     <t>прессе?</t>
   </si>
   <si>
-    <t>физического</t>
-  </si>
-  <si>
     <t>эпитаксиально</t>
   </si>
   <si>
@@ -510,12 +423,6 @@
     <t>энергетически</t>
   </si>
   <si>
-    <t>модулирует</t>
-  </si>
-  <si>
-    <t>модулятора</t>
-  </si>
-  <si>
     <t>сотрапезники</t>
   </si>
   <si>
@@ -540,9 +447,6 @@
     <t>энергоинформационные меридианы</t>
   </si>
   <si>
-    <t>Информационный</t>
-  </si>
-  <si>
     <t>дециметровом</t>
   </si>
   <si>
@@ -627,12 +531,6 @@
     <t>дискета</t>
   </si>
   <si>
-    <t>визуализировать</t>
-  </si>
-  <si>
-    <t>протогалактика</t>
-  </si>
-  <si>
     <t>гранаты</t>
   </si>
   <si>
@@ -642,12 +540,6 @@
     <t>статуя</t>
   </si>
   <si>
-    <t>журналах</t>
-  </si>
-  <si>
-    <t>газетах</t>
-  </si>
-  <si>
     <t>артиллерии</t>
   </si>
   <si>
@@ -708,12 +600,6 @@
     <t>технократического </t>
   </si>
   <si>
-    <t xml:space="preserve">материализма </t>
-  </si>
-  <si>
-    <t>бумеранг</t>
-  </si>
-  <si>
     <t>энергетики</t>
   </si>
   <si>
@@ -742,9 +628,6 @@
   </si>
   <si>
     <t xml:space="preserve">спиновую </t>
-  </si>
-  <si>
-    <t xml:space="preserve">материальности </t>
   </si>
   <si>
     <t>изменилась при</t>
@@ -1100,49 +983,49 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F21563D1-1294-476A-895B-8DF86C2F507F}">
   <dimension ref="A2:C41"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="43" customWidth="1"/>
-    <col min="2" max="2" width="14.42578125" customWidth="1"/>
+    <col min="2" max="2" width="14.453125" customWidth="1"/>
     <col min="3" max="3" width="33" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>146</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>184</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>147</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>163</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>183</v>
+        <v>152</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>233</v>
+        <v>195</v>
       </c>
       <c r="C41" t="s">
-        <v>234</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -1153,1192 +1036,955 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F65167D-C510-40BD-B401-AA5A335D9CBB}">
   <dimension ref="A2:B278"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="29.28515625" customWidth="1"/>
+    <col min="1" max="1" width="29.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>135</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>136</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>169</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>200</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>187</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>212</v>
+        <v>177</v>
       </c>
       <c r="B16" t="s">
-        <v>213</v>
+        <v>178</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>205</v>
+        <v>170</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>138</v>
+        <v>111</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" t="s">
-        <v>129</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>203</v>
+        <v>105</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" t="s">
-        <v>126</v>
+        <v>168</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" t="s">
-        <v>166</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>100</v>
+        <v>135</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>208</v>
+        <v>88</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>47</v>
+        <v>149</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" t="s">
-        <v>96</v>
+        <v>37</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>165</v>
+        <v>56</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>115</v>
+        <v>162</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>192</v>
+        <v>76</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>179</v>
+        <v>134</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>198</v>
+        <v>91</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>123</v>
+        <v>161</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1">
-      <c r="A46" t="s">
-        <v>23</v>
+        <v>148</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>44</v>
+        <v>99</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>15</v>
+        <v>87</v>
       </c>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="3" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" t="s">
-        <v>160</v>
+      <c r="A49" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>114</v>
+        <v>11</v>
       </c>
     </row>
     <row r="52" spans="1:1">
-      <c r="A52" t="s">
-        <v>12</v>
+      <c r="A52" s="3" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1">
-      <c r="A54" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1">
-      <c r="A55" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1">
-      <c r="A56" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1">
-      <c r="A57" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1">
-      <c r="A58" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1">
-      <c r="A59" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1">
-      <c r="A60" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>31</v>
+        <v>136</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" t="s">
-        <v>30</v>
+        <v>98</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>28</v>
+        <v>86</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" t="s">
-        <v>137</v>
+        <v>25</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" t="s">
-        <v>90</v>
+        <v>25</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" t="s">
-        <v>189</v>
+        <v>23</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" t="s">
-        <v>143</v>
+        <v>22</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" t="s">
-        <v>145</v>
+        <v>110</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" t="s">
-        <v>128</v>
+        <v>71</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" t="s">
-        <v>111</v>
+        <v>158</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" t="s">
-        <v>148</v>
+        <v>116</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" t="s">
-        <v>83</v>
+        <v>118</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" t="s">
-        <v>152</v>
+        <v>104</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" t="s">
-        <v>58</v>
+        <v>89</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1">
-      <c r="A77" t="s">
-        <v>38</v>
+        <v>121</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" t="s">
-        <v>34</v>
+        <v>182</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1">
-      <c r="A82" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1">
-      <c r="A83" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1">
-      <c r="A84" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1">
-      <c r="A85" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1">
-      <c r="A86" t="s">
-        <v>134</v>
+        <v>181</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" t="s">
-        <v>65</v>
+        <v>29</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89" t="s">
-        <v>46</v>
+        <v>142</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" t="s">
-        <v>133</v>
+        <v>19</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1">
-      <c r="A92" t="s">
-        <v>154</v>
+        <v>100</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1">
-      <c r="A94" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1">
-      <c r="A95" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
     </row>
     <row r="96" spans="1:1">
       <c r="A96" t="s">
-        <v>141</v>
+        <v>180</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98" t="s">
-        <v>94</v>
+        <v>36</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="100" spans="1:1">
-      <c r="A100" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="101" spans="1:1">
-      <c r="A101" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="102" spans="1:1">
-      <c r="A102" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="103" spans="1:1">
-      <c r="A103" t="s">
-        <v>170</v>
+        <v>107</v>
       </c>
     </row>
     <row r="104" spans="1:1">
       <c r="A104" t="s">
-        <v>45</v>
+        <v>183</v>
       </c>
     </row>
     <row r="105" spans="1:1">
       <c r="A105" t="s">
-        <v>186</v>
+        <v>31</v>
       </c>
     </row>
     <row r="106" spans="1:1">
       <c r="A106" t="s">
-        <v>158</v>
+        <v>114</v>
       </c>
     </row>
     <row r="107" spans="1:1">
       <c r="A107" t="s">
-        <v>69</v>
+        <v>32</v>
       </c>
     </row>
     <row r="108" spans="1:1">
       <c r="A108" t="s">
-        <v>177</v>
+        <v>74</v>
       </c>
     </row>
     <row r="109" spans="1:1">
       <c r="A109" t="s">
-        <v>112</v>
+        <v>67</v>
       </c>
     </row>
     <row r="110" spans="1:1">
       <c r="A110" t="s">
-        <v>35</v>
+        <v>112</v>
       </c>
     </row>
     <row r="111" spans="1:1">
       <c r="A111" t="s">
-        <v>6</v>
+        <v>93</v>
       </c>
     </row>
     <row r="112" spans="1:1">
       <c r="A112" t="s">
-        <v>0</v>
+        <v>169</v>
       </c>
     </row>
     <row r="113" spans="1:1">
       <c r="A113" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="114" spans="1:1">
-      <c r="A114" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
     </row>
     <row r="115" spans="1:1">
       <c r="A115" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
     </row>
     <row r="116" spans="1:1">
       <c r="A116" t="s">
-        <v>76</v>
+        <v>155</v>
       </c>
     </row>
     <row r="117" spans="1:1">
       <c r="A117" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
     </row>
     <row r="118" spans="1:1">
       <c r="A118" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="119" spans="1:1">
-      <c r="A119" t="s">
-        <v>87</v>
+        <v>54</v>
       </c>
     </row>
     <row r="120" spans="1:1">
       <c r="A120" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="121" spans="1:1">
-      <c r="A121" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="122" spans="1:1">
-      <c r="A122" t="s">
-        <v>104</v>
+        <v>146</v>
       </c>
     </row>
     <row r="123" spans="1:1">
       <c r="A123" t="s">
-        <v>89</v>
+        <v>4</v>
       </c>
     </row>
     <row r="124" spans="1:1">
       <c r="A124" t="s">
-        <v>84</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:1">
       <c r="A125" t="s">
-        <v>209</v>
+        <v>15</v>
       </c>
     </row>
     <row r="126" spans="1:1">
       <c r="A126" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="127" spans="1:1">
-      <c r="A127" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="128" spans="1:1">
-      <c r="A128" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="129" spans="1:1">
-      <c r="A129" t="s">
-        <v>42</v>
+        <v>97</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" t="s">
-        <v>149</v>
+        <v>117</v>
       </c>
     </row>
     <row r="131" spans="1:1">
       <c r="A131" t="s">
-        <v>26</v>
+        <v>69</v>
       </c>
     </row>
     <row r="132" spans="1:1">
       <c r="A132" t="s">
-        <v>62</v>
+        <v>140</v>
       </c>
     </row>
     <row r="133" spans="1:1">
       <c r="A133" t="s">
-        <v>194</v>
+        <v>79</v>
       </c>
     </row>
     <row r="134" spans="1:1">
       <c r="A134" t="s">
-        <v>37</v>
+        <v>82</v>
       </c>
     </row>
     <row r="135" spans="1:1">
       <c r="A135" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
     </row>
     <row r="136" spans="1:1">
       <c r="A136" t="s">
-        <v>125</v>
+        <v>66</v>
       </c>
     </row>
     <row r="137" spans="1:1">
       <c r="A137" t="s">
-        <v>191</v>
+        <v>174</v>
       </c>
     </row>
     <row r="138" spans="1:1">
       <c r="A138" t="s">
-        <v>196</v>
+        <v>48</v>
       </c>
     </row>
     <row r="139" spans="1:1">
       <c r="A139" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
     </row>
     <row r="140" spans="1:1">
       <c r="A140" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
     </row>
     <row r="141" spans="1:1">
       <c r="A141" t="s">
-        <v>201</v>
+        <v>34</v>
       </c>
     </row>
     <row r="142" spans="1:1">
       <c r="A142" t="s">
-        <v>175</v>
+        <v>122</v>
       </c>
     </row>
     <row r="143" spans="1:1">
       <c r="A143" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="144" spans="1:1">
       <c r="A144" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="145" spans="1:1">
-      <c r="A145" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="146" spans="1:1">
-      <c r="A146" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
     </row>
     <row r="147" spans="1:1">
       <c r="A147" t="s">
-        <v>131</v>
+        <v>30</v>
       </c>
     </row>
     <row r="148" spans="1:1">
       <c r="A148" t="s">
-        <v>172</v>
+        <v>101</v>
       </c>
     </row>
     <row r="149" spans="1:1">
       <c r="A149" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="150" spans="1:1">
       <c r="A150" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
     </row>
     <row r="151" spans="1:1">
       <c r="A151" t="s">
-        <v>156</v>
+        <v>12</v>
       </c>
     </row>
     <row r="152" spans="1:1">
       <c r="A152" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="153" spans="1:1">
       <c r="A153" t="s">
-        <v>22</v>
+        <v>166</v>
       </c>
     </row>
     <row r="154" spans="1:1">
       <c r="A154" t="s">
-        <v>70</v>
+        <v>144</v>
       </c>
     </row>
     <row r="155" spans="1:1">
       <c r="A155" t="s">
-        <v>78</v>
+        <v>10</v>
       </c>
     </row>
     <row r="156" spans="1:1">
       <c r="A156" t="s">
-        <v>68</v>
+        <v>143</v>
       </c>
     </row>
     <row r="157" spans="1:1">
       <c r="A157" t="s">
-        <v>59</v>
+        <v>84</v>
       </c>
     </row>
     <row r="158" spans="1:1">
       <c r="A158" t="s">
-        <v>210</v>
+        <v>50</v>
       </c>
     </row>
     <row r="159" spans="1:1">
       <c r="A159" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="160" spans="1:1">
       <c r="A160" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="161" spans="1:1">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
       <c r="A161" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2">
+      <c r="A166" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2">
+      <c r="A167" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2">
+      <c r="A168" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2">
+      <c r="A169" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2">
+      <c r="A170" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2">
+      <c r="A171" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2">
+      <c r="A173" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2">
+      <c r="A175" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2">
+      <c r="A176" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="162" spans="1:1">
-      <c r="A162" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="163" spans="1:1">
-      <c r="A163" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="164" spans="1:1">
-      <c r="A164" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="165" spans="1:1">
-      <c r="A165" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="166" spans="1:1">
-      <c r="A166" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="167" spans="1:1">
-      <c r="A167" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="168" spans="1:1">
-      <c r="A168" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="169" spans="1:1">
-      <c r="A169" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="170" spans="1:1">
-      <c r="A170" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="171" spans="1:1">
-      <c r="A171" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="172" spans="1:1">
-      <c r="A172" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="173" spans="1:1">
-      <c r="A173" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="174" spans="1:1">
-      <c r="A174" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="175" spans="1:1">
-      <c r="A175" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="176" spans="1:1">
-      <c r="A176" t="s">
-        <v>150</v>
+      <c r="B176" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="177" spans="1:1">
-      <c r="A177" s="1" t="s">
-        <v>1</v>
+      <c r="A177" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="178" spans="1:1">
       <c r="A178" t="s">
-        <v>11</v>
+        <v>137</v>
       </c>
     </row>
     <row r="179" spans="1:1">
       <c r="A179" t="s">
-        <v>130</v>
+        <v>78</v>
       </c>
     </row>
     <row r="180" spans="1:1">
       <c r="A180" t="s">
-        <v>43</v>
+        <v>78</v>
       </c>
     </row>
     <row r="181" spans="1:1">
       <c r="A181" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
     </row>
     <row r="182" spans="1:1">
       <c r="A182" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
     </row>
     <row r="183" spans="1:1">
       <c r="A183" t="s">
-        <v>113</v>
+        <v>64</v>
       </c>
     </row>
     <row r="184" spans="1:1">
       <c r="A184" t="s">
-        <v>73</v>
+        <v>147</v>
       </c>
     </row>
     <row r="185" spans="1:1">
       <c r="A185" t="s">
-        <v>75</v>
+        <v>151</v>
       </c>
     </row>
     <row r="186" spans="1:1">
       <c r="A186" t="s">
-        <v>60</v>
+        <v>150</v>
       </c>
     </row>
     <row r="187" spans="1:1">
       <c r="A187" t="s">
-        <v>202</v>
+        <v>154</v>
       </c>
     </row>
     <row r="188" spans="1:1">
       <c r="A188" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="189" spans="1:1">
-      <c r="A189" t="s">
-        <v>51</v>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1" ht="17.5">
+      <c r="A189" s="4" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="190" spans="1:1">
       <c r="A190" t="s">
-        <v>5</v>
+        <v>188</v>
       </c>
     </row>
     <row r="191" spans="1:1">
       <c r="A191" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
     </row>
     <row r="192" spans="1:1">
       <c r="A192" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="193" spans="1:1">
-      <c r="A193" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="194" spans="1:1">
-      <c r="A194" t="s">
-        <v>32</v>
+        <v>83</v>
       </c>
     </row>
     <row r="195" spans="1:1">
-      <c r="A195" t="s">
-        <v>49</v>
-      </c>
+      <c r="A195" s="1"/>
     </row>
     <row r="196" spans="1:1">
       <c r="A196" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
     </row>
     <row r="197" spans="1:1">
       <c r="A197" t="s">
-        <v>3</v>
+        <v>68</v>
       </c>
     </row>
     <row r="198" spans="1:1">
       <c r="A198" t="s">
-        <v>176</v>
+        <v>90</v>
       </c>
     </row>
     <row r="199" spans="1:1">
       <c r="A199" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
     </row>
     <row r="200" spans="1:1">
       <c r="A200" t="s">
-        <v>153</v>
+        <v>192</v>
       </c>
     </row>
     <row r="201" spans="1:1">
       <c r="A201" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
     </row>
     <row r="202" spans="1:1">
       <c r="A202" t="s">
-        <v>116</v>
+        <v>47</v>
       </c>
     </row>
     <row r="203" spans="1:1">
       <c r="A203" t="s">
-        <v>206</v>
+        <v>167</v>
       </c>
     </row>
     <row r="204" spans="1:1">
       <c r="A204" t="s">
-        <v>9</v>
+        <v>58</v>
       </c>
     </row>
     <row r="205" spans="1:1">
       <c r="A205" t="s">
-        <v>211</v>
+        <v>193</v>
       </c>
     </row>
     <row r="206" spans="1:1">
       <c r="A206" t="s">
-        <v>159</v>
+        <v>40</v>
       </c>
     </row>
     <row r="207" spans="1:1">
       <c r="A207" t="s">
-        <v>188</v>
+        <v>3</v>
       </c>
     </row>
     <row r="208" spans="1:1">
       <c r="A208" t="s">
-        <v>142</v>
+        <v>72</v>
       </c>
     </row>
     <row r="209" spans="1:1">
       <c r="A209" t="s">
-        <v>151</v>
+        <v>94</v>
       </c>
     </row>
     <row r="210" spans="1:1">
       <c r="A210" t="s">
-        <v>161</v>
+        <v>45</v>
       </c>
     </row>
     <row r="211" spans="1:1">
       <c r="A211" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
     </row>
     <row r="212" spans="1:1">
       <c r="A212" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="213" spans="1:1">
       <c r="A213" t="s">
-        <v>215</v>
+        <v>60</v>
       </c>
     </row>
     <row r="214" spans="1:1">
       <c r="A214" t="s">
-        <v>216</v>
+        <v>1</v>
       </c>
     </row>
     <row r="215" spans="1:1">
       <c r="A215" t="s">
-        <v>217</v>
+        <v>145</v>
       </c>
     </row>
     <row r="216" spans="1:1">
       <c r="A216" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="217" spans="1:1" ht="18">
-      <c r="A217" s="4" t="s">
-        <v>219</v>
+        <v>185</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1">
+      <c r="A217" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="218" spans="1:1">
       <c r="A218" t="s">
-        <v>220</v>
+        <v>125</v>
       </c>
     </row>
     <row r="219" spans="1:1">
       <c r="A219" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
     </row>
     <row r="220" spans="1:1">
       <c r="A220" t="s">
-        <v>221</v>
+        <v>186</v>
       </c>
     </row>
     <row r="221" spans="1:1">
       <c r="A221" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
     </row>
     <row r="222" spans="1:1">
       <c r="A222" t="s">
-        <v>222</v>
+        <v>171</v>
       </c>
     </row>
     <row r="223" spans="1:1">
       <c r="A223" t="s">
-        <v>223</v>
+        <v>6</v>
       </c>
     </row>
     <row r="224" spans="1:1">
       <c r="A224" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="225" spans="1:2">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1">
       <c r="A225" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="226" spans="1:2">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1">
       <c r="A226" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="227" spans="1:2">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1">
       <c r="A227" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="228" spans="1:2">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1">
       <c r="A228" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="229" spans="1:2">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1">
       <c r="A229" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="230" spans="1:2">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1">
       <c r="A230" t="s">
-        <v>227</v>
-      </c>
-      <c r="B230" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="231" spans="1:2">
-      <c r="A231" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="232" spans="1:2">
-      <c r="A232" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="233" spans="1:2">
-      <c r="A233" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="234" spans="1:2">
-      <c r="A234" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="235" spans="1:2">
-      <c r="A235" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="278" spans="1:1" ht="15.75">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="278" spans="1:1" ht="15.5">
       <c r="A278" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:B211" xr:uid="{1F65167D-C510-40BD-B401-AA5A335D9CBB}"/>
+  <autoFilter ref="A2:B278" xr:uid="{1F65167D-C510-40BD-B401-AA5A335D9CBB}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B278">
     <sortCondition ref="A2:A278"/>
   </sortState>
@@ -2350,11 +1996,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4792E377-39EC-4785-9269-9C61E9BFD62D}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>207</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -2365,11 +2011,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DBA598F-779B-4000-A874-2A5A01A11567}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>197</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -2380,14 +2026,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B672A3D-6BD1-4167-A6FD-CFAEF2ED5EE0}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="20.140625" customWidth="1"/>
+    <col min="1" max="1" width="20.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>214</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>

--- a/исправления внести/эниология.xlsx
+++ b/исправления внести/эниология.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\исправления внести\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\исправления внести\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DD8FC9E-9DA8-4133-8543-9671E1EDE223}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C075887B-FDDB-4A45-8647-D0E4600BC8DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25510" yWindow="0" windowWidth="12980" windowHeight="20970" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="после перевода" sheetId="2" r:id="rId1"/>
@@ -38,12 +38,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="209">
   <si>
     <t>оперативная группа</t>
   </si>
@@ -634,6 +637,42 @@
   </si>
   <si>
     <t>изменился при</t>
+  </si>
+  <si>
+    <t>открытая прообраз</t>
+  </si>
+  <si>
+    <t>телескопом</t>
+  </si>
+  <si>
+    <t xml:space="preserve">призму </t>
+  </si>
+  <si>
+    <t>уровня тепла звёзд.</t>
+  </si>
+  <si>
+    <t>Главной последовательности чертёж-рисунки</t>
+  </si>
+  <si>
+    <t>нашей Созвездия</t>
+  </si>
+  <si>
+    <t>Центр Созвездия</t>
+  </si>
+  <si>
+    <t>Ось созвездия</t>
+  </si>
+  <si>
+    <t xml:space="preserve">спектрограмм </t>
+  </si>
+  <si>
+    <t xml:space="preserve">эффектом </t>
+  </si>
+  <si>
+    <t xml:space="preserve">фиксировал </t>
+  </si>
+  <si>
+    <t>прообраз Фридмана получила широкое распространение</t>
   </si>
 </sst>
 </file>
@@ -983,10 +1022,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F21563D1-1294-476A-895B-8DF86C2F507F}">
   <dimension ref="A2:C41"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="43" customWidth="1"/>
-    <col min="2" max="2" width="14.453125" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" customWidth="1"/>
     <col min="3" max="3" width="33" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1010,6 +1049,16 @@
         <v>120</v>
       </c>
     </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>197</v>
+      </c>
+    </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
         <v>133</v>
@@ -1018,6 +1067,21 @@
     <row r="15" spans="1:1">
       <c r="A15" t="s">
         <v>152</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1036,9 +1100,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F65167D-C510-40BD-B401-AA5A335D9CBB}">
   <dimension ref="A2:B278"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="29.26953125" customWidth="1"/>
+    <col min="1" max="1" width="29.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:2">
@@ -1782,7 +1846,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="189" spans="1:1" ht="17.5">
+    <row r="189" spans="1:1" ht="18">
       <c r="A189" s="4" t="s">
         <v>184</v>
       </c>
@@ -1980,7 +2044,32 @@
         <v>38</v>
       </c>
     </row>
-    <row r="278" spans="1:1" ht="15.5">
+    <row r="231" spans="1:1">
+      <c r="A231" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1">
+      <c r="A232" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1">
+      <c r="A233" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1">
+      <c r="A234" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1">
+      <c r="A235" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="278" spans="1:1" ht="15.75">
       <c r="A278" s="2"/>
     </row>
   </sheetData>
@@ -1996,7 +2085,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4792E377-39EC-4785-9269-9C61E9BFD62D}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
@@ -2010,12 +2099,20 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DBA598F-779B-4000-A874-2A5A01A11567}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>164</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B2" t="s">
+        <v>204</v>
       </c>
     </row>
   </sheetData>
@@ -2026,9 +2123,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B672A3D-6BD1-4167-A6FD-CFAEF2ED5EE0}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="20.1796875" customWidth="1"/>
+    <col min="1" max="1" width="20.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
